--- a/projects/cost-data/raw-images/_output/output/Kopi-av-239-B-AA-001_10_001.xlsx
+++ b/projects/cost-data/raw-images/_output/output/Kopi-av-239-B-AA-001_10_001.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monthly report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Budget" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,36 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B0000"/>
+        <bgColor rgb="008B0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +69,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,417 +443,205 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="54" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Document template: PRO1-FM-Arkill, Rev. 25, Dato: 18.06.2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MONTHLY REPORT</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>bulk</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Bulk infrastructure by BDC Build Estate AS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BUDGET REPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Type of budget:</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Construction project budget</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Yellow background = OFFICIAL, awaiting on contract signature with CTS</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PROJECT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PRO1 - Pegasus phase 2</t>
+          <t>Bulk company:</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BDC Real Estate #1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Red text = changed from last time</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PROJECT MANAGER</t>
+          <t>Version:</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OVERALL PROJECT STATUS: BDC DETACH3 BULDGE</t>
+          <t>Periode:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BDC - under decisions to plan</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>95,64% delivered to plan</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>GROSS: up to</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>01.04.26</t>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Status plan defined success criteria</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Priority</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Comments if any</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Time (S %)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Major</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>UNCERTAIN: LECA activities pending extra Kapitalises</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HSE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>2023-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report per:</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1 april 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>COST ELEMENT</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Budget</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Reestimate</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Budget with allowance</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Reestimate (CTRL)
+pr rap.report date</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>payment</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>cumulated</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Expected invoiced
+pr report date</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Remaining
+to be</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Report(s)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Contractual End</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>New Baseline</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Budget/result/plan</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>BCWS Cumulative EA (to date)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Budget</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Payment details</t>
-        </is>
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>54618.71</v>
+      </c>
+      <c r="E14" t="n">
+        <v>134483.71</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Infrastructure &amp; Final Construction Design Review Complete</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>02.02.2023</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>02.02.2023</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Budgeted</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1007160</v>
+          <t>CTS safety (CRC RC 18)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>991121985</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wells Floors (Signal LI) og ventil</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>08.02.2023</t>
-        </is>
+          <t>CTS milestone penalties</t>
+        </is>
+      </c>
+      <c r="F16" s="5">
+        <f>D16+E16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Building Available for Client Works</t>
+          <t>D&amp;B incl (HK sales)</t>
         </is>
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="n">
+        <v>110</v>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Networks rooms clean and available for Client works</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>06.06.2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Customer SE Mechanical Ready Include</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>15.09.2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Completed UPS Installation complete</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>20.03.2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Customer 122 Mechanisk Party Access</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>20.12.2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>White Block, completed</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>30.11.2025</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>30.11.2025</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>PROJECT COST</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1607126</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Ventils Block, completed / 1/4 signed off all</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Draft CQIs issued</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>01.11.2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CQua issued no final P84</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>30.11.2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Praktisk ferdigstillelse</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>10.02.2025</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1489000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>10.02.2025</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2560</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>IMPORTANT ISSUES/PROBLEMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>UNCERTAIN: to reflect the constructive milestones and current status/internal/External focus</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>CTS performance per today not adequate and being mopped by Project team - to make sure they recover adequately/plan follows up</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Remaining M3 CL4 + c2b5 (4) to be submitted as soon as schedules are completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>UNCERTAIN: constructional flexibility/other considerations safely/as required</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>CTS performance declining reference to Q1, Q2, Q4, Bulk position is that CTS is responsible for completing work/safely/to code</t>
+          <t>Incomes ERBs and EDU losses</t>
         </is>
       </c>
     </row>
